--- a/docs/Example Files/CRYSS V2.0 Input File Templates/9 Component Mixture.xlsx
+++ b/docs/Example Files/CRYSS V2.0 Input File Templates/9 Component Mixture.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\06 website\idiocratease-iggy.github.io\docs\Example Files\CRYSS V2.0 Input File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8147C71-F2D6-458D-924C-105689B8DA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC684D3-B16A-406D-B39A-E63B44D93226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="225" windowWidth="48060" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="300" windowWidth="31980" windowHeight="16116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="slice_records" sheetId="1" r:id="rId1"/>
+    <sheet name="CRYSS Input File V2.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -259,24 +259,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -284,12 +290,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -595,59 +595,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="18" customWidth="1"/>
-    <col min="30" max="34" width="12.5703125" customWidth="1"/>
+    <col min="30" max="34" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="11" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="8" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="14" t="s">
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="16"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="18"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -731,26 +731,26 @@
       <c r="AB2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="17" t="s">
+      <c r="AC2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AE2" s="18" t="s">
+      <c r="AE2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AF2" s="18" t="s">
+      <c r="AF2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="AG2" s="18" t="s">
+      <c r="AG2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AH2" s="18" t="s">
+      <c r="AH2" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -784,7 +784,7 @@
       <c r="AF3" s="6"/>
       <c r="AH3" s="7"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -818,7 +818,7 @@
       <c r="AF4" s="6"/>
       <c r="AH4" s="7"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -852,7 +852,7 @@
       <c r="AF5" s="6"/>
       <c r="AH5" s="7"/>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -886,7 +886,7 @@
       <c r="AF6" s="6"/>
       <c r="AH6" s="7"/>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -920,7 +920,7 @@
       <c r="AF7" s="6"/>
       <c r="AH7" s="7"/>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -954,7 +954,7 @@
       <c r="AF8" s="6"/>
       <c r="AH8" s="7"/>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -988,7 +988,7 @@
       <c r="AF9" s="6"/>
       <c r="AH9" s="7"/>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1022,7 +1022,7 @@
       <c r="AF10" s="6"/>
       <c r="AH10" s="7"/>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1056,7 +1056,7 @@
       <c r="AF11" s="6"/>
       <c r="AH11" s="7"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1090,7 +1090,7 @@
       <c r="AF12" s="6"/>
       <c r="AH12" s="7"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1124,7 +1124,7 @@
       <c r="AF13" s="6"/>
       <c r="AH13" s="7"/>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1158,70 +1158,70 @@
       <c r="AF14" s="6"/>
       <c r="AH14" s="7"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="AC15" s="5"/>
       <c r="AD15" s="6"/>
       <c r="AE15" s="5"/>
       <c r="AF15" s="6"/>
       <c r="AH15" s="7"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="AC16" s="5"/>
       <c r="AD16" s="6"/>
       <c r="AE16" s="5"/>
       <c r="AF16" s="6"/>
       <c r="AH16" s="7"/>
     </row>
-    <row r="17" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC17" s="5"/>
       <c r="AD17" s="6"/>
       <c r="AE17" s="5"/>
       <c r="AF17" s="6"/>
       <c r="AH17" s="7"/>
     </row>
-    <row r="18" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC18" s="5"/>
       <c r="AD18" s="6"/>
       <c r="AE18" s="5"/>
       <c r="AF18" s="6"/>
       <c r="AH18" s="7"/>
     </row>
-    <row r="19" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC19" s="5"/>
       <c r="AD19" s="6"/>
       <c r="AE19" s="5"/>
       <c r="AF19" s="6"/>
       <c r="AH19" s="7"/>
     </row>
-    <row r="20" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC20" s="5"/>
       <c r="AD20" s="6"/>
       <c r="AE20" s="5"/>
       <c r="AF20" s="6"/>
       <c r="AH20" s="7"/>
     </row>
-    <row r="21" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC21" s="5"/>
       <c r="AD21" s="6"/>
       <c r="AE21" s="5"/>
       <c r="AF21" s="6"/>
       <c r="AH21" s="7"/>
     </row>
-    <row r="22" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC22" s="5"/>
       <c r="AD22" s="6"/>
       <c r="AE22" s="5"/>
       <c r="AF22" s="6"/>
       <c r="AH22" s="7"/>
     </row>
-    <row r="23" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC23" s="5"/>
       <c r="AD23" s="6"/>
       <c r="AE23" s="5"/>
       <c r="AF23" s="6"/>
       <c r="AH23" s="7"/>
     </row>
-    <row r="24" spans="29:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="29:34" x14ac:dyDescent="0.3">
       <c r="AC24" s="5"/>
       <c r="AD24" s="6"/>
       <c r="AE24" s="5"/>
